--- a/LoanOfficer-A/2023/145 moirangthem bijenty.xlsx
+++ b/LoanOfficer-A/2023/145 moirangthem bijenty.xlsx
@@ -819,7 +819,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -828,7 +828,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)+SUM(C34:C63)+SUM(G34:G63)+SUM(K34:K63)+SUM(O34:O63)+SUM(C65:C94)</f>
-        <v>1400</v>
+        <v>4200</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -857,7 +857,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)+SUM(D34:D63)+SUM(H34:H63)+SUM(P34:P63)+SUM(D65:D91)+SUM(L34:L63)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -866,7 +866,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>22400</v>
+        <v>19600</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -906,9 +906,15 @@
       <c r="A4" s="1">
         <v>2</v>
       </c>
-      <c r="B4" s="3"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="1"/>
+      <c r="B4" s="3">
+        <v>45981</v>
+      </c>
+      <c r="C4" s="4">
+        <v>1400</v>
+      </c>
+      <c r="D4" s="1">
+        <v>1</v>
+      </c>
       <c r="E4" s="1">
         <v>32</v>
       </c>
@@ -932,9 +938,15 @@
       <c r="A5" s="1">
         <v>3</v>
       </c>
-      <c r="B5" s="3"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="1"/>
+      <c r="B5" s="3">
+        <v>45985</v>
+      </c>
+      <c r="C5" s="4">
+        <v>1400</v>
+      </c>
+      <c r="D5" s="1">
+        <v>1</v>
+      </c>
       <c r="E5" s="1">
         <v>33</v>
       </c>

--- a/LoanOfficer-A/2023/145 moirangthem bijenty.xlsx
+++ b/LoanOfficer-A/2023/145 moirangthem bijenty.xlsx
@@ -819,7 +819,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -828,7 +828,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)+SUM(C34:C63)+SUM(G34:G63)+SUM(K34:K63)+SUM(O34:O63)+SUM(C65:C94)</f>
-        <v>4200</v>
+        <v>7000</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -857,7 +857,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)+SUM(D34:D63)+SUM(H34:H63)+SUM(P34:P63)+SUM(D65:D91)+SUM(L34:L63)</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -866,7 +866,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>19600</v>
+        <v>16800</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -970,9 +970,15 @@
       <c r="A6" s="1">
         <v>4</v>
       </c>
-      <c r="B6" s="3"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="1"/>
+      <c r="B6" s="3">
+        <v>45997</v>
+      </c>
+      <c r="C6" s="4">
+        <v>1400</v>
+      </c>
+      <c r="D6" s="1">
+        <v>1</v>
+      </c>
       <c r="E6" s="1">
         <v>34</v>
       </c>
@@ -996,9 +1002,15 @@
       <c r="A7" s="1">
         <v>5</v>
       </c>
-      <c r="B7" s="3"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="1"/>
+      <c r="B7" s="3">
+        <v>45997</v>
+      </c>
+      <c r="C7" s="4">
+        <v>1400</v>
+      </c>
+      <c r="D7" s="1">
+        <v>1</v>
+      </c>
       <c r="E7" s="1">
         <v>35</v>
       </c>

--- a/LoanOfficer-A/2023/145 moirangthem bijenty.xlsx
+++ b/LoanOfficer-A/2023/145 moirangthem bijenty.xlsx
@@ -14,7 +14,7 @@
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'MD50000.15-DEC'!$A$3:$N$32</definedName>
   </definedNames>
-  <calcPr calcId="162913" iterateDelta="1E-4"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -819,7 +819,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -828,7 +828,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)+SUM(C34:C63)+SUM(G34:G63)+SUM(K34:K63)+SUM(O34:O63)+SUM(C65:C94)</f>
-        <v>7000</v>
+        <v>9800</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -857,7 +857,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)+SUM(D34:D63)+SUM(H34:H63)+SUM(P34:P63)+SUM(D65:D91)+SUM(L34:L63)</f>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -866,7 +866,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>16800</v>
+        <v>14000</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -1034,9 +1034,15 @@
       <c r="A8" s="1">
         <v>6</v>
       </c>
-      <c r="B8" s="3"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="1"/>
+      <c r="B8" s="3">
+        <v>46019</v>
+      </c>
+      <c r="C8" s="4">
+        <v>1400</v>
+      </c>
+      <c r="D8" s="1">
+        <v>1</v>
+      </c>
       <c r="E8" s="1">
         <v>36</v>
       </c>
@@ -1060,9 +1066,15 @@
       <c r="A9" s="1">
         <v>7</v>
       </c>
-      <c r="B9" s="3"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="1"/>
+      <c r="B9" s="3">
+        <v>46019</v>
+      </c>
+      <c r="C9" s="4">
+        <v>1400</v>
+      </c>
+      <c r="D9" s="1">
+        <v>1</v>
+      </c>
       <c r="E9" s="1">
         <v>37</v>
       </c>
